--- a/backend/signal_logs/backfill_reports/complete_report_2026-08-21_to_2026-08-28.xlsx
+++ b/backend/signal_logs/backfill_reports/complete_report_2026-08-21_to_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="53" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3725,6 +3725,435 @@
         <v>14.57</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Closed down ~305.45 (-3.4% from entry)</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Closed up ~12.85 (+7.5% from entry)</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>16.41</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Closed up ~12.1 (+1.3% from entry)</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Closed up ~21.55 (+9.4% from entry)</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Closed down ~10.8 (-9.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>-9.6</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>16.41</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Closed flat ~25.3 (+0.0% from entry)</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>16.87</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Closed down ~17.55 (-10.9% from entry, EOD estimate)</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>-10.9</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Closed flat ~34.8 (+0.0% from entry)</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>253.35</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Closed down ~249.05 (-1.7% from entry, EOD estimate)</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
